--- a/GATEWAY/A1#111#FLORENSCODESRLXX/FLORENS_CODE_SRL/CONSENSOSICURO/1.0.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111#FLORENSCODESRLXX/FLORENS_CODE_SRL/CONSENSOSICURO/1.0.0/report-checklist.xlsx
@@ -2701,10 +2701,14 @@
       </c>
       <c r="K10" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L10" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L10" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M10" s="32" t="n"/>
       <c r="N10" s="32" t="n"/>
       <c r="O10" s="32" t="n"/>
@@ -2760,10 +2764,14 @@
       </c>
       <c r="K11" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L11" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L11" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M11" s="32" t="n"/>
       <c r="N11" s="32" t="n"/>
       <c r="O11" s="32" t="n"/>
@@ -2819,10 +2827,14 @@
       </c>
       <c r="K12" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L12" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L12" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M12" s="32" t="n"/>
       <c r="N12" s="32" t="n"/>
       <c r="O12" s="32" t="n"/>
@@ -2878,10 +2890,14 @@
       </c>
       <c r="K13" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L13" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L13" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M13" s="32" t="n"/>
       <c r="N13" s="32" t="n"/>
       <c r="O13" s="32" t="n"/>
@@ -2937,10 +2953,14 @@
       </c>
       <c r="K14" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L14" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L14" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M14" s="32" t="n"/>
       <c r="N14" s="32" t="n"/>
       <c r="O14" s="32" t="n"/>
@@ -2996,7 +3016,7 @@
       </c>
       <c r="K15" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>Campo valorizzato di default</t>
         </is>
       </c>
       <c r="L15" s="32" t="n"/>
@@ -3055,10 +3075,14 @@
       </c>
       <c r="K16" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L16" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L16" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M16" s="32" t="n"/>
       <c r="N16" s="32" t="n"/>
       <c r="O16" s="32" t="n"/>
@@ -3114,10 +3138,14 @@
       </c>
       <c r="K17" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L17" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L17" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M17" s="32" t="n"/>
       <c r="N17" s="32" t="n"/>
       <c r="O17" s="32" t="n"/>
@@ -3173,10 +3201,14 @@
       </c>
       <c r="K18" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L18" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L18" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M18" s="32" t="n"/>
       <c r="N18" s="32" t="n"/>
       <c r="O18" s="32" t="n"/>
@@ -3232,10 +3264,14 @@
       </c>
       <c r="K19" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L19" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L19" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M19" s="32" t="n"/>
       <c r="N19" s="32" t="n"/>
       <c r="O19" s="32" t="n"/>
@@ -3291,10 +3327,14 @@
       </c>
       <c r="K20" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L20" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L20" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M20" s="32" t="n"/>
       <c r="N20" s="32" t="n"/>
       <c r="O20" s="32" t="n"/>
@@ -3350,10 +3390,14 @@
       </c>
       <c r="K21" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L21" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L21" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M21" s="32" t="n"/>
       <c r="N21" s="32" t="n"/>
       <c r="O21" s="32" t="n"/>
@@ -3409,10 +3453,14 @@
       </c>
       <c r="K22" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L22" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L22" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M22" s="32" t="n"/>
       <c r="N22" s="32" t="n"/>
       <c r="O22" s="32" t="n"/>
@@ -3468,7 +3516,7 @@
       </c>
       <c r="K23" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>Campo valorizzato di default</t>
         </is>
       </c>
       <c r="L23" s="32" t="n"/>
@@ -3527,10 +3575,14 @@
       </c>
       <c r="K24" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L24" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L24" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M24" s="32" t="n"/>
       <c r="N24" s="32" t="n"/>
       <c r="O24" s="32" t="n"/>
@@ -3586,10 +3638,14 @@
       </c>
       <c r="K25" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L25" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L25" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M25" s="32" t="n"/>
       <c r="N25" s="32" t="n"/>
       <c r="O25" s="32" t="n"/>
@@ -3645,10 +3701,14 @@
       </c>
       <c r="K26" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L26" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L26" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M26" s="32" t="n"/>
       <c r="N26" s="32" t="n"/>
       <c r="O26" s="32" t="n"/>
@@ -3701,10 +3761,14 @@
       </c>
       <c r="K27" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L27" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L27" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M27" s="32" t="n"/>
       <c r="N27" s="32" t="n"/>
       <c r="O27" s="32" t="n"/>
@@ -3761,10 +3825,14 @@
       </c>
       <c r="K28" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L28" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L28" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M28" s="32" t="n"/>
       <c r="N28" s="32" t="n"/>
       <c r="O28" s="32" t="n"/>
@@ -3821,10 +3889,14 @@
       </c>
       <c r="K29" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L29" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L29" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M29" s="32" t="n"/>
       <c r="N29" s="32" t="n"/>
       <c r="O29" s="32" t="n"/>
@@ -3881,10 +3953,14 @@
       </c>
       <c r="K30" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L30" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L30" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M30" s="32" t="n"/>
       <c r="N30" s="32" t="n"/>
       <c r="O30" s="32" t="n"/>
@@ -3941,17 +4017,49 @@
       </c>
       <c r="K31" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
-        </is>
-      </c>
-      <c r="L31" s="32" t="n"/>
-      <c r="M31" s="32" t="n"/>
-      <c r="N31" s="32" t="n"/>
-      <c r="O31" s="32" t="n"/>
-      <c r="P31" s="32" t="n"/>
-      <c r="Q31" s="32" t="n"/>
-      <c r="R31" s="32" t="n"/>
-      <c r="S31" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L31" s="32" t="inlineStr">
+        <is>
+          <t>Scenario di timeout non riproducibile a comando sul gateway di pre-produzione. La gestione applicativa del timeout è comunque implementata e descritta nelle colonne di gestione errore: invio asincrono con coda di retry automatica e possibilità di reinvio manuale.</t>
+        </is>
+      </c>
+      <c r="M31" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N31" s="32" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="O31" s="32" t="inlineStr">
+        <is>
+          <t>Badge di stato FSE sulla visita: «In coda di invio» durante i tentativi automatici; in caso di scarto definitivo «Rifiutato» con dettaglio dell'errore e pulsante «Riprova invio».</t>
+        </is>
+      </c>
+      <c r="P31" s="32" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="Q31" s="32" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="R31" s="32" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="S31" s="32" t="inlineStr">
+        <is>
+          <t>L'invio al gateway è asincrono e non bloccante: il medico completa la visita e produce il documento anche se il servizio non è raggiungibile. In caso di timeout il documento resta in coda (stato QUEUED/SIGNED) e il job di trasmissione lo ritenta automaticamente ogni 5 minuti fino al ripristino del servizio. In caso di errore definitivo il documento passa in stato REJECTED, visibile all'utente con il dettaglio dell'errore e reinvio manuale tramite pulsante «Riprova invio» dopo la risoluzione; i documenti in errore sono inoltre monitorati in backoffice dal fornitore.</t>
+        </is>
+      </c>
       <c r="T31" s="32" t="n"/>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -4001,10 +4109,14 @@
       </c>
       <c r="K32" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L32" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L32" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M32" s="32" t="n"/>
       <c r="N32" s="32" t="n"/>
       <c r="O32" s="32" t="n"/>
@@ -4061,10 +4173,14 @@
       </c>
       <c r="K33" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L33" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L33" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M33" s="32" t="n"/>
       <c r="N33" s="32" t="n"/>
       <c r="O33" s="32" t="n"/>
@@ -4121,10 +4237,14 @@
       </c>
       <c r="K34" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L34" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L34" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M34" s="32" t="n"/>
       <c r="N34" s="32" t="n"/>
       <c r="O34" s="32" t="n"/>
@@ -4181,10 +4301,14 @@
       </c>
       <c r="K35" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L35" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L35" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M35" s="32" t="n"/>
       <c r="N35" s="32" t="n"/>
       <c r="O35" s="32" t="n"/>
@@ -4237,10 +4361,14 @@
       </c>
       <c r="K36" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L36" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L36" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M36" s="32" t="n"/>
       <c r="N36" s="32" t="n"/>
       <c r="O36" s="32" t="n"/>
@@ -4293,10 +4421,14 @@
       </c>
       <c r="K37" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L37" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L37" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M37" s="32" t="n"/>
       <c r="N37" s="32" t="n"/>
       <c r="O37" s="32" t="n"/>
@@ -4349,10 +4481,14 @@
       </c>
       <c r="K38" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L38" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L38" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M38" s="32" t="n"/>
       <c r="N38" s="32" t="n"/>
       <c r="O38" s="32" t="n"/>
@@ -4405,10 +4541,14 @@
       </c>
       <c r="K39" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L39" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L39" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M39" s="32" t="n"/>
       <c r="N39" s="32" t="n"/>
       <c r="O39" s="32" t="n"/>
@@ -4461,10 +4601,14 @@
       </c>
       <c r="K40" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L40" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L40" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M40" s="32" t="n"/>
       <c r="N40" s="32" t="n"/>
       <c r="O40" s="32" t="n"/>
@@ -4517,10 +4661,14 @@
       </c>
       <c r="K41" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L41" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L41" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M41" s="32" t="n"/>
       <c r="N41" s="32" t="n"/>
       <c r="O41" s="32" t="n"/>
@@ -4573,10 +4721,14 @@
       </c>
       <c r="K42" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L42" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L42" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M42" s="32" t="n"/>
       <c r="N42" s="32" t="n"/>
       <c r="O42" s="32" t="n"/>
@@ -4629,10 +4781,14 @@
       </c>
       <c r="K43" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L43" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L43" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M43" s="32" t="n"/>
       <c r="N43" s="32" t="n"/>
       <c r="O43" s="32" t="n"/>
@@ -4685,10 +4841,14 @@
       </c>
       <c r="K44" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L44" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L44" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M44" s="32" t="n"/>
       <c r="N44" s="32" t="n"/>
       <c r="O44" s="32" t="n"/>
@@ -4741,10 +4901,14 @@
       </c>
       <c r="K45" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L45" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L45" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M45" s="32" t="n"/>
       <c r="N45" s="32" t="n"/>
       <c r="O45" s="32" t="n"/>
@@ -4797,10 +4961,14 @@
       </c>
       <c r="K46" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L46" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L46" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M46" s="32" t="n"/>
       <c r="N46" s="32" t="n"/>
       <c r="O46" s="32" t="n"/>
@@ -4853,10 +5021,14 @@
       </c>
       <c r="K47" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L47" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L47" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M47" s="32" t="n"/>
       <c r="N47" s="32" t="n"/>
       <c r="O47" s="32" t="n"/>
@@ -4909,10 +5081,14 @@
       </c>
       <c r="K48" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L48" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L48" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M48" s="32" t="n"/>
       <c r="N48" s="32" t="n"/>
       <c r="O48" s="32" t="n"/>
@@ -4965,10 +5141,14 @@
       </c>
       <c r="K49" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L49" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L49" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M49" s="32" t="n"/>
       <c r="N49" s="32" t="n"/>
       <c r="O49" s="32" t="n"/>
@@ -5021,10 +5201,14 @@
       </c>
       <c r="K50" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L50" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L50" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M50" s="32" t="n"/>
       <c r="N50" s="32" t="n"/>
       <c r="O50" s="32" t="n"/>
@@ -5077,10 +5261,14 @@
       </c>
       <c r="K51" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L51" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L51" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M51" s="32" t="n"/>
       <c r="N51" s="32" t="n"/>
       <c r="O51" s="32" t="n"/>
@@ -5133,10 +5321,14 @@
       </c>
       <c r="K52" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L52" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L52" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M52" s="32" t="n"/>
       <c r="N52" s="32" t="n"/>
       <c r="O52" s="32" t="n"/>
@@ -5189,10 +5381,14 @@
       </c>
       <c r="K53" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L53" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L53" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M53" s="32" t="n"/>
       <c r="N53" s="32" t="n"/>
       <c r="O53" s="32" t="n"/>
@@ -5245,10 +5441,14 @@
       </c>
       <c r="K54" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L54" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L54" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M54" s="32" t="n"/>
       <c r="N54" s="32" t="n"/>
       <c r="O54" s="32" t="n"/>
@@ -5301,10 +5501,14 @@
       </c>
       <c r="K55" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L55" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L55" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M55" s="32" t="n"/>
       <c r="N55" s="32" t="n"/>
       <c r="O55" s="32" t="n"/>
@@ -5357,10 +5561,14 @@
       </c>
       <c r="K56" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L56" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L56" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M56" s="32" t="n"/>
       <c r="N56" s="32" t="n"/>
       <c r="O56" s="32" t="n"/>
@@ -5413,10 +5621,14 @@
       </c>
       <c r="K57" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L57" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L57" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M57" s="32" t="n"/>
       <c r="N57" s="32" t="n"/>
       <c r="O57" s="32" t="n"/>
@@ -5469,10 +5681,14 @@
       </c>
       <c r="K58" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L58" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L58" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M58" s="32" t="n"/>
       <c r="N58" s="32" t="n"/>
       <c r="O58" s="32" t="n"/>
@@ -5525,10 +5741,14 @@
       </c>
       <c r="K59" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L59" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L59" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M59" s="32" t="n"/>
       <c r="N59" s="32" t="n"/>
       <c r="O59" s="32" t="n"/>
@@ -5581,10 +5801,14 @@
       </c>
       <c r="K60" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L60" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L60" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M60" s="32" t="n"/>
       <c r="N60" s="32" t="n"/>
       <c r="O60" s="32" t="n"/>
@@ -5637,10 +5861,14 @@
       </c>
       <c r="K61" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L61" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L61" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M61" s="32" t="n"/>
       <c r="N61" s="32" t="n"/>
       <c r="O61" s="32" t="n"/>
@@ -5693,10 +5921,14 @@
       </c>
       <c r="K62" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L62" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L62" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M62" s="32" t="n"/>
       <c r="N62" s="32" t="n"/>
       <c r="O62" s="32" t="n"/>
@@ -5749,10 +5981,14 @@
       </c>
       <c r="K63" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L63" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L63" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M63" s="32" t="n"/>
       <c r="N63" s="32" t="n"/>
       <c r="O63" s="32" t="n"/>
@@ -5805,10 +6041,14 @@
       </c>
       <c r="K64" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L64" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L64" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M64" s="32" t="n"/>
       <c r="N64" s="32" t="n"/>
       <c r="O64" s="32" t="n"/>
@@ -5861,10 +6101,14 @@
       </c>
       <c r="K65" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L65" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L65" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M65" s="32" t="n"/>
       <c r="N65" s="32" t="n"/>
       <c r="O65" s="32" t="n"/>
@@ -5917,10 +6161,14 @@
       </c>
       <c r="K66" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L66" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L66" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M66" s="32" t="n"/>
       <c r="N66" s="32" t="n"/>
       <c r="O66" s="32" t="n"/>
@@ -5973,10 +6221,14 @@
       </c>
       <c r="K67" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L67" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L67" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M67" s="32" t="n"/>
       <c r="N67" s="32" t="n"/>
       <c r="O67" s="32" t="n"/>
@@ -6029,10 +6281,14 @@
       </c>
       <c r="K68" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L68" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L68" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M68" s="32" t="n"/>
       <c r="N68" s="32" t="n"/>
       <c r="O68" s="32" t="n"/>
@@ -6085,10 +6341,14 @@
       </c>
       <c r="K69" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L69" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L69" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M69" s="32" t="n"/>
       <c r="N69" s="32" t="n"/>
       <c r="O69" s="32" t="n"/>
@@ -6141,10 +6401,14 @@
       </c>
       <c r="K70" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M70" s="32" t="n"/>
       <c r="N70" s="32" t="n"/>
       <c r="O70" s="32" t="n"/>
@@ -6197,10 +6461,14 @@
       </c>
       <c r="K71" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L71" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M71" s="32" t="n"/>
       <c r="N71" s="32" t="n"/>
       <c r="O71" s="32" t="n"/>
@@ -6253,10 +6521,14 @@
       </c>
       <c r="K72" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M72" s="32" t="n"/>
       <c r="N72" s="32" t="n"/>
       <c r="O72" s="32" t="n"/>
@@ -6309,10 +6581,14 @@
       </c>
       <c r="K73" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M73" s="32" t="n"/>
       <c r="N73" s="32" t="n"/>
       <c r="O73" s="32" t="n"/>
@@ -6365,10 +6641,14 @@
       </c>
       <c r="K74" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M74" s="32" t="n"/>
       <c r="N74" s="32" t="n"/>
       <c r="O74" s="32" t="n"/>
@@ -6421,10 +6701,14 @@
       </c>
       <c r="K75" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L75" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L75" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M75" s="32" t="n"/>
       <c r="N75" s="32" t="n"/>
       <c r="O75" s="32" t="n"/>
@@ -6477,10 +6761,14 @@
       </c>
       <c r="K76" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L76" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L76" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M76" s="32" t="n"/>
       <c r="N76" s="32" t="n"/>
       <c r="O76" s="32" t="n"/>
@@ -6533,10 +6821,14 @@
       </c>
       <c r="K77" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L77" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L77" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M77" s="32" t="n"/>
       <c r="N77" s="32" t="n"/>
       <c r="O77" s="32" t="n"/>
@@ -6589,10 +6881,14 @@
       </c>
       <c r="K78" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L78" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M78" s="32" t="n"/>
       <c r="N78" s="32" t="n"/>
       <c r="O78" s="32" t="n"/>
@@ -6645,10 +6941,14 @@
       </c>
       <c r="K79" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L79" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M79" s="32" t="n"/>
       <c r="N79" s="32" t="n"/>
       <c r="O79" s="32" t="n"/>
@@ -6701,10 +7001,14 @@
       </c>
       <c r="K80" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L80" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M80" s="32" t="n"/>
       <c r="N80" s="32" t="n"/>
       <c r="O80" s="32" t="n"/>
@@ -6757,10 +7061,14 @@
       </c>
       <c r="K81" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L81" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L81" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M81" s="32" t="n"/>
       <c r="N81" s="32" t="n"/>
       <c r="O81" s="32" t="n"/>
@@ -6813,10 +7121,14 @@
       </c>
       <c r="K82" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L82" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M82" s="32" t="n"/>
       <c r="N82" s="32" t="n"/>
       <c r="O82" s="32" t="n"/>
@@ -6869,10 +7181,14 @@
       </c>
       <c r="K83" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L83" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L83" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M83" s="32" t="n"/>
       <c r="N83" s="32" t="n"/>
       <c r="O83" s="32" t="n"/>
@@ -6925,10 +7241,14 @@
       </c>
       <c r="K84" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L84" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L84" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M84" s="32" t="n"/>
       <c r="N84" s="32" t="n"/>
       <c r="O84" s="32" t="n"/>
@@ -6981,10 +7301,14 @@
       </c>
       <c r="K85" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L85" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L85" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M85" s="32" t="n"/>
       <c r="N85" s="32" t="n"/>
       <c r="O85" s="32" t="n"/>
@@ -7037,10 +7361,14 @@
       </c>
       <c r="K86" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L86" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L86" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M86" s="32" t="n"/>
       <c r="N86" s="32" t="n"/>
       <c r="O86" s="32" t="n"/>
@@ -7093,10 +7421,14 @@
       </c>
       <c r="K87" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L87" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L87" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M87" s="32" t="n"/>
       <c r="N87" s="32" t="n"/>
       <c r="O87" s="32" t="n"/>
@@ -7149,10 +7481,14 @@
       </c>
       <c r="K88" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L88" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L88" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M88" s="32" t="n"/>
       <c r="N88" s="32" t="n"/>
       <c r="O88" s="32" t="n"/>
@@ -7205,10 +7541,14 @@
       </c>
       <c r="K89" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L89" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L89" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M89" s="32" t="n"/>
       <c r="N89" s="32" t="n"/>
       <c r="O89" s="32" t="n"/>
@@ -7261,10 +7601,14 @@
       </c>
       <c r="K90" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L90" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L90" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M90" s="32" t="n"/>
       <c r="N90" s="32" t="n"/>
       <c r="O90" s="32" t="n"/>
@@ -7317,10 +7661,14 @@
       </c>
       <c r="K91" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L91" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L91" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M91" s="32" t="n"/>
       <c r="N91" s="32" t="n"/>
       <c r="O91" s="32" t="n"/>
@@ -7373,10 +7721,14 @@
       </c>
       <c r="K92" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L92" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L92" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M92" s="32" t="n"/>
       <c r="N92" s="32" t="n"/>
       <c r="O92" s="32" t="n"/>
@@ -7429,10 +7781,14 @@
       </c>
       <c r="K93" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L93" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L93" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M93" s="32" t="n"/>
       <c r="N93" s="32" t="n"/>
       <c r="O93" s="32" t="n"/>
@@ -7485,10 +7841,14 @@
       </c>
       <c r="K94" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L94" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L94" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M94" s="32" t="n"/>
       <c r="N94" s="32" t="n"/>
       <c r="O94" s="32" t="n"/>
@@ -7541,10 +7901,14 @@
       </c>
       <c r="K95" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L95" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L95" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M95" s="32" t="n"/>
       <c r="N95" s="32" t="n"/>
       <c r="O95" s="32" t="n"/>
@@ -7597,10 +7961,14 @@
       </c>
       <c r="K96" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L96" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L96" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M96" s="32" t="n"/>
       <c r="N96" s="32" t="n"/>
       <c r="O96" s="32" t="n"/>
@@ -7653,10 +8021,14 @@
       </c>
       <c r="K97" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L97" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L97" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M97" s="32" t="n"/>
       <c r="N97" s="32" t="n"/>
       <c r="O97" s="32" t="n"/>
@@ -7709,10 +8081,14 @@
       </c>
       <c r="K98" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L98" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L98" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M98" s="32" t="n"/>
       <c r="N98" s="32" t="n"/>
       <c r="O98" s="32" t="n"/>
@@ -7765,10 +8141,14 @@
       </c>
       <c r="K99" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L99" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L99" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M99" s="32" t="n"/>
       <c r="N99" s="32" t="n"/>
       <c r="O99" s="32" t="n"/>
@@ -7821,10 +8201,14 @@
       </c>
       <c r="K100" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L100" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L100" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M100" s="32" t="n"/>
       <c r="N100" s="32" t="n"/>
       <c r="O100" s="32" t="n"/>
@@ -7877,10 +8261,14 @@
       </c>
       <c r="K101" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L101" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L101" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M101" s="32" t="n"/>
       <c r="N101" s="32" t="n"/>
       <c r="O101" s="32" t="n"/>
@@ -7933,10 +8321,14 @@
       </c>
       <c r="K102" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L102" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L102" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M102" s="32" t="n"/>
       <c r="N102" s="32" t="n"/>
       <c r="O102" s="32" t="n"/>
@@ -7989,10 +8381,14 @@
       </c>
       <c r="K103" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L103" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L103" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M103" s="32" t="n"/>
       <c r="N103" s="32" t="n"/>
       <c r="O103" s="32" t="n"/>
@@ -8045,10 +8441,14 @@
       </c>
       <c r="K104" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L104" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L104" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M104" s="32" t="n"/>
       <c r="N104" s="32" t="n"/>
       <c r="O104" s="32" t="n"/>
@@ -8101,10 +8501,14 @@
       </c>
       <c r="K105" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L105" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L105" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M105" s="32" t="n"/>
       <c r="N105" s="32" t="n"/>
       <c r="O105" s="32" t="n"/>
@@ -8157,10 +8561,14 @@
       </c>
       <c r="K106" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L106" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L106" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M106" s="32" t="n"/>
       <c r="N106" s="32" t="n"/>
       <c r="O106" s="32" t="n"/>
@@ -8213,10 +8621,14 @@
       </c>
       <c r="K107" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L107" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L107" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M107" s="32" t="n"/>
       <c r="N107" s="32" t="n"/>
       <c r="O107" s="32" t="n"/>
@@ -8269,10 +8681,14 @@
       </c>
       <c r="K108" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L108" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L108" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M108" s="32" t="n"/>
       <c r="N108" s="32" t="n"/>
       <c r="O108" s="32" t="n"/>
@@ -8325,10 +8741,14 @@
       </c>
       <c r="K109" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L109" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L109" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M109" s="32" t="n"/>
       <c r="N109" s="32" t="n"/>
       <c r="O109" s="32" t="n"/>
@@ -8381,10 +8801,14 @@
       </c>
       <c r="K110" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L110" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L110" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M110" s="32" t="n"/>
       <c r="N110" s="32" t="n"/>
       <c r="O110" s="32" t="n"/>
@@ -8437,10 +8861,14 @@
       </c>
       <c r="K111" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L111" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L111" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M111" s="32" t="n"/>
       <c r="N111" s="32" t="n"/>
       <c r="O111" s="32" t="n"/>
@@ -8493,10 +8921,14 @@
       </c>
       <c r="K112" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L112" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L112" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M112" s="32" t="n"/>
       <c r="N112" s="32" t="n"/>
       <c r="O112" s="32" t="n"/>
@@ -8549,10 +8981,14 @@
       </c>
       <c r="K113" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L113" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L113" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M113" s="32" t="n"/>
       <c r="N113" s="32" t="n"/>
       <c r="O113" s="32" t="n"/>
@@ -8605,10 +9041,14 @@
       </c>
       <c r="K114" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L114" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L114" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M114" s="32" t="n"/>
       <c r="N114" s="32" t="n"/>
       <c r="O114" s="32" t="n"/>
@@ -8661,10 +9101,14 @@
       </c>
       <c r="K115" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L115" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L115" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M115" s="32" t="n"/>
       <c r="N115" s="32" t="n"/>
       <c r="O115" s="32" t="n"/>
@@ -8717,7 +9161,7 @@
       </c>
       <c r="K116" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>L’applicativo effettua controlli preventivi sul dato inserito</t>
         </is>
       </c>
       <c r="L116" s="32" t="n"/>
@@ -8773,7 +9217,7 @@
       </c>
       <c r="K117" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>L’applicativo effettua controlli preventivi sul dato inserito</t>
         </is>
       </c>
       <c r="L117" s="32" t="n"/>
@@ -8829,7 +9273,7 @@
       </c>
       <c r="K118" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>L’applicativo effettua controlli preventivi sul dato inserito</t>
         </is>
       </c>
       <c r="L118" s="32" t="n"/>
@@ -8885,7 +9329,7 @@
       </c>
       <c r="K119" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>L’applicativo effettua controlli preventivi sul dato inserito</t>
         </is>
       </c>
       <c r="L119" s="32" t="n"/>
@@ -8941,7 +9385,7 @@
       </c>
       <c r="K120" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>L’applicativo effettua controlli preventivi sul dato inserito</t>
         </is>
       </c>
       <c r="L120" s="32" t="n"/>
@@ -8997,7 +9441,7 @@
       </c>
       <c r="K121" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>L’applicativo effettua controlli preventivi sul dato inserito</t>
         </is>
       </c>
       <c r="L121" s="32" t="n"/>
@@ -9053,7 +9497,7 @@
       </c>
       <c r="K122" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>L’applicativo effettua controlli preventivi sul dato inserito</t>
         </is>
       </c>
       <c r="L122" s="32" t="n"/>
@@ -9109,7 +9553,7 @@
       </c>
       <c r="K123" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>L’applicativo effettua controlli preventivi sul dato inserito</t>
         </is>
       </c>
       <c r="L123" s="32" t="n"/>
@@ -9165,7 +9609,7 @@
       </c>
       <c r="K124" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>L’applicativo effettua controlli preventivi sul dato inserito</t>
         </is>
       </c>
       <c r="L124" s="32" t="n"/>
@@ -9221,7 +9665,7 @@
       </c>
       <c r="K125" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>L’applicativo effettua controlli preventivi sul dato inserito</t>
         </is>
       </c>
       <c r="L125" s="32" t="n"/>
@@ -9277,7 +9721,7 @@
       </c>
       <c r="K126" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>L’applicativo effettua controlli preventivi sul dato inserito</t>
         </is>
       </c>
       <c r="L126" s="32" t="n"/>
@@ -9333,7 +9777,7 @@
       </c>
       <c r="K127" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>L’applicativo effettua controlli preventivi sul dato inserito</t>
         </is>
       </c>
       <c r="L127" s="32" t="n"/>
@@ -9389,7 +9833,7 @@
       </c>
       <c r="K128" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>L’applicativo effettua controlli preventivi sul dato inserito</t>
         </is>
       </c>
       <c r="L128" s="32" t="n"/>
@@ -9445,7 +9889,7 @@
       </c>
       <c r="K129" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>L’applicativo effettua controlli preventivi sul dato inserito</t>
         </is>
       </c>
       <c r="L129" s="32" t="n"/>
@@ -9501,7 +9945,7 @@
       </c>
       <c r="K130" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>L’applicativo effettua controlli preventivi sul dato inserito</t>
         </is>
       </c>
       <c r="L130" s="32" t="n"/>
@@ -9557,10 +10001,14 @@
       </c>
       <c r="K131" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L131" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L131" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M131" s="32" t="n"/>
       <c r="N131" s="32" t="n"/>
       <c r="O131" s="32" t="n"/>
@@ -9613,10 +10061,14 @@
       </c>
       <c r="K132" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L132" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L132" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M132" s="32" t="n"/>
       <c r="N132" s="32" t="n"/>
       <c r="O132" s="32" t="n"/>
@@ -9669,10 +10121,14 @@
       </c>
       <c r="K133" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L133" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L133" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M133" s="32" t="n"/>
       <c r="N133" s="32" t="n"/>
       <c r="O133" s="32" t="n"/>
@@ -9725,10 +10181,14 @@
       </c>
       <c r="K134" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L134" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L134" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M134" s="32" t="n"/>
       <c r="N134" s="32" t="n"/>
       <c r="O134" s="32" t="n"/>
@@ -9781,10 +10241,14 @@
       </c>
       <c r="K135" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L135" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L135" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M135" s="32" t="n"/>
       <c r="N135" s="32" t="n"/>
       <c r="O135" s="32" t="n"/>
@@ -9837,10 +10301,14 @@
       </c>
       <c r="K136" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L136" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L136" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M136" s="32" t="n"/>
       <c r="N136" s="32" t="n"/>
       <c r="O136" s="32" t="n"/>
@@ -9893,10 +10361,14 @@
       </c>
       <c r="K137" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L137" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L137" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M137" s="32" t="n"/>
       <c r="N137" s="32" t="n"/>
       <c r="O137" s="32" t="n"/>
@@ -9949,10 +10421,14 @@
       </c>
       <c r="K138" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L138" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L138" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M138" s="32" t="n"/>
       <c r="N138" s="32" t="n"/>
       <c r="O138" s="32" t="n"/>
@@ -10005,10 +10481,14 @@
       </c>
       <c r="K139" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L139" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L139" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M139" s="32" t="n"/>
       <c r="N139" s="32" t="n"/>
       <c r="O139" s="32" t="n"/>
@@ -10061,10 +10541,14 @@
       </c>
       <c r="K140" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L140" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L140" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M140" s="32" t="n"/>
       <c r="N140" s="32" t="n"/>
       <c r="O140" s="32" t="n"/>
@@ -10117,10 +10601,14 @@
       </c>
       <c r="K141" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L141" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L141" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M141" s="32" t="n"/>
       <c r="N141" s="32" t="n"/>
       <c r="O141" s="32" t="n"/>
@@ -10173,10 +10661,14 @@
       </c>
       <c r="K142" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L142" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L142" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M142" s="32" t="n"/>
       <c r="N142" s="32" t="n"/>
       <c r="O142" s="32" t="n"/>
@@ -10229,10 +10721,14 @@
       </c>
       <c r="K143" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L143" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L143" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M143" s="32" t="n"/>
       <c r="N143" s="32" t="n"/>
       <c r="O143" s="32" t="n"/>
@@ -10285,10 +10781,14 @@
       </c>
       <c r="K144" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L144" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L144" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M144" s="32" t="n"/>
       <c r="N144" s="32" t="n"/>
       <c r="O144" s="32" t="n"/>
@@ -10341,10 +10841,14 @@
       </c>
       <c r="K145" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L145" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L145" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M145" s="32" t="n"/>
       <c r="N145" s="32" t="n"/>
       <c r="O145" s="32" t="n"/>
@@ -10398,10 +10902,14 @@
       </c>
       <c r="K146" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L146" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L146" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M146" s="32" t="n"/>
       <c r="N146" s="32" t="n"/>
       <c r="O146" s="32" t="n"/>
@@ -10455,10 +10963,14 @@
       </c>
       <c r="K147" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L147" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L147" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M147" s="32" t="n"/>
       <c r="N147" s="32" t="n"/>
       <c r="O147" s="32" t="n"/>
@@ -10511,10 +11023,14 @@
       </c>
       <c r="K148" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L148" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L148" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M148" s="32" t="n"/>
       <c r="N148" s="32" t="n"/>
       <c r="O148" s="32" t="n"/>
@@ -10568,10 +11084,14 @@
       </c>
       <c r="K149" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L149" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L149" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M149" s="32" t="n"/>
       <c r="N149" s="32" t="n"/>
       <c r="O149" s="32" t="n"/>
@@ -10625,10 +11145,14 @@
       </c>
       <c r="K150" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L150" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L150" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M150" s="32" t="n"/>
       <c r="N150" s="32" t="n"/>
       <c r="O150" s="32" t="n"/>
@@ -10684,10 +11208,14 @@
       </c>
       <c r="K151" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L151" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L151" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M151" s="32" t="n"/>
       <c r="N151" s="32" t="n"/>
       <c r="O151" s="32" t="n"/>
@@ -10743,10 +11271,14 @@
       </c>
       <c r="K152" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L152" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L152" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M152" s="32" t="n"/>
       <c r="N152" s="32" t="n"/>
       <c r="O152" s="32" t="n"/>
@@ -10799,10 +11331,14 @@
       </c>
       <c r="K153" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L153" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L153" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M153" s="32" t="n"/>
       <c r="N153" s="32" t="n"/>
       <c r="O153" s="32" t="n"/>
@@ -10859,10 +11395,14 @@
       </c>
       <c r="K154" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L154" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L154" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M154" s="32" t="n"/>
       <c r="N154" s="32" t="n"/>
       <c r="O154" s="32" t="n"/>
@@ -10915,10 +11455,14 @@
       </c>
       <c r="K155" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L155" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L155" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M155" s="32" t="n"/>
       <c r="N155" s="32" t="n"/>
       <c r="O155" s="32" t="n"/>
@@ -10971,10 +11515,14 @@
       </c>
       <c r="K156" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L156" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L156" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M156" s="32" t="n"/>
       <c r="N156" s="32" t="n"/>
       <c r="O156" s="32" t="n"/>
@@ -11027,10 +11575,14 @@
       </c>
       <c r="K157" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L157" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L157" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M157" s="32" t="n"/>
       <c r="N157" s="32" t="n"/>
       <c r="O157" s="32" t="n"/>
@@ -11083,10 +11635,14 @@
       </c>
       <c r="K158" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L158" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L158" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M158" s="32" t="n"/>
       <c r="N158" s="32" t="n"/>
       <c r="O158" s="32" t="n"/>
@@ -11139,10 +11695,14 @@
       </c>
       <c r="K159" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L159" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L159" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M159" s="32" t="n"/>
       <c r="N159" s="32" t="n"/>
       <c r="O159" s="32" t="n"/>
@@ -11195,10 +11755,14 @@
       </c>
       <c r="K160" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L160" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L160" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M160" s="32" t="n"/>
       <c r="N160" s="32" t="n"/>
       <c r="O160" s="32" t="n"/>
@@ -11251,10 +11815,14 @@
       </c>
       <c r="K161" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L161" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L161" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M161" s="32" t="n"/>
       <c r="N161" s="32" t="n"/>
       <c r="O161" s="32" t="n"/>
@@ -11307,10 +11875,14 @@
       </c>
       <c r="K162" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L162" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L162" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M162" s="32" t="n"/>
       <c r="N162" s="32" t="n"/>
       <c r="O162" s="32" t="n"/>
@@ -11363,10 +11935,14 @@
       </c>
       <c r="K163" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L163" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L163" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M163" s="32" t="n"/>
       <c r="N163" s="32" t="n"/>
       <c r="O163" s="32" t="n"/>
@@ -11491,7 +12067,7 @@
       </c>
       <c r="K165" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>Campo/sezione non gestito/a in modo strutturato dall’applicativo</t>
         </is>
       </c>
       <c r="L165" s="32" t="n"/>
@@ -11547,10 +12123,14 @@
       </c>
       <c r="K166" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L166" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L166" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M166" s="32" t="n"/>
       <c r="N166" s="32" t="n"/>
       <c r="O166" s="32" t="n"/>
@@ -11603,10 +12183,14 @@
       </c>
       <c r="K167" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L167" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L167" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M167" s="32" t="n"/>
       <c r="N167" s="32" t="n"/>
       <c r="O167" s="32" t="n"/>
@@ -11660,10 +12244,14 @@
       </c>
       <c r="K168" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L168" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L168" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M168" s="32" t="n"/>
       <c r="N168" s="32" t="n"/>
       <c r="O168" s="32" t="n"/>
@@ -11716,10 +12304,14 @@
       </c>
       <c r="K169" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L169" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L169" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M169" s="32" t="n"/>
       <c r="N169" s="32" t="n"/>
       <c r="O169" s="32" t="n"/>
@@ -11772,10 +12364,14 @@
       </c>
       <c r="K170" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L170" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L170" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M170" s="32" t="n"/>
       <c r="N170" s="32" t="n"/>
       <c r="O170" s="32" t="n"/>
@@ -11828,10 +12424,14 @@
       </c>
       <c r="K171" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L171" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L171" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M171" s="32" t="n"/>
       <c r="N171" s="32" t="n"/>
       <c r="O171" s="32" t="n"/>
@@ -11884,10 +12484,14 @@
       </c>
       <c r="K172" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L172" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L172" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M172" s="32" t="n"/>
       <c r="N172" s="32" t="n"/>
       <c r="O172" s="32" t="n"/>
@@ -11940,10 +12544,14 @@
       </c>
       <c r="K173" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L173" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L173" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M173" s="32" t="n"/>
       <c r="N173" s="32" t="n"/>
       <c r="O173" s="32" t="n"/>
@@ -11996,10 +12604,14 @@
       </c>
       <c r="K174" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L174" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L174" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M174" s="32" t="n"/>
       <c r="N174" s="32" t="n"/>
       <c r="O174" s="32" t="n"/>
@@ -12052,10 +12664,14 @@
       </c>
       <c r="K175" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L175" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L175" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M175" s="32" t="n"/>
       <c r="N175" s="32" t="n"/>
       <c r="O175" s="32" t="n"/>
@@ -12108,7 +12724,7 @@
       </c>
       <c r="K176" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>Campo/sezione non gestito/a in modo strutturato dall’applicativo</t>
         </is>
       </c>
       <c r="L176" s="29" t="n"/>
@@ -12164,10 +12780,14 @@
       </c>
       <c r="K177" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L177" s="29" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L177" s="29" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M177" s="32" t="n"/>
       <c r="N177" s="32" t="n"/>
       <c r="O177" s="29" t="n"/>
@@ -12220,10 +12840,14 @@
       </c>
       <c r="K178" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L178" s="29" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L178" s="29" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M178" s="32" t="n"/>
       <c r="N178" s="32" t="n"/>
       <c r="O178" s="29" t="n"/>
@@ -12276,10 +12900,14 @@
       </c>
       <c r="K179" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L179" s="29" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L179" s="29" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M179" s="32" t="n"/>
       <c r="N179" s="32" t="n"/>
       <c r="O179" s="29" t="n"/>
@@ -12332,10 +12960,14 @@
       </c>
       <c r="K180" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L180" s="29" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L180" s="29" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M180" s="32" t="n"/>
       <c r="N180" s="32" t="n"/>
       <c r="O180" s="29" t="n"/>
@@ -12388,10 +13020,14 @@
       </c>
       <c r="K181" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L181" s="29" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L181" s="29" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M181" s="32" t="n"/>
       <c r="N181" s="32" t="n"/>
       <c r="O181" s="29" t="n"/>
@@ -12444,10 +13080,14 @@
       </c>
       <c r="K182" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L182" s="29" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L182" s="29" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M182" s="32" t="n"/>
       <c r="N182" s="32" t="n"/>
       <c r="O182" s="29" t="n"/>
@@ -12500,7 +13140,7 @@
       </c>
       <c r="K183" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>Campo/sezione non gestito/a in modo strutturato dall’applicativo</t>
         </is>
       </c>
       <c r="L183" s="29" t="n"/>
@@ -12556,10 +13196,14 @@
       </c>
       <c r="K184" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L184" s="29" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L184" s="29" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M184" s="32" t="n"/>
       <c r="N184" s="32" t="n"/>
       <c r="O184" s="29" t="n"/>
@@ -12612,10 +13256,14 @@
       </c>
       <c r="K185" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L185" s="29" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L185" s="29" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M185" s="32" t="n"/>
       <c r="N185" s="32" t="n"/>
       <c r="O185" s="29" t="n"/>
@@ -12668,10 +13316,14 @@
       </c>
       <c r="K186" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L186" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L186" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M186" s="32" t="n"/>
       <c r="N186" s="32" t="n"/>
       <c r="O186" s="32" t="n"/>
@@ -12724,10 +13376,14 @@
       </c>
       <c r="K187" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L187" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L187" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M187" s="32" t="n"/>
       <c r="N187" s="32" t="n"/>
       <c r="O187" s="32" t="n"/>
@@ -12780,10 +13436,14 @@
       </c>
       <c r="K188" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L188" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L188" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M188" s="32" t="n"/>
       <c r="N188" s="32" t="n"/>
       <c r="O188" s="32" t="n"/>
@@ -12836,10 +13496,14 @@
       </c>
       <c r="K189" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L189" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L189" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M189" s="32" t="n"/>
       <c r="N189" s="32" t="n"/>
       <c r="O189" s="32" t="n"/>
@@ -12892,7 +13556,7 @@
       </c>
       <c r="K190" s="32" t="inlineStr">
         <is>
-          <t>ConsensoSicuro genera CDA2 RSA in conformita' al template HL7 Italia v8.3 con scenario minimo (test 448 - CT24). Scenari piu' articolati (CT25, KO cases con strutture nidificate organizer/observation per allergie, terapia farmacologica, anamnesi clinica strutturata) non sono coperti dalla v1.0.0; la gestione errore avviene tramite stato REJECTED del documento e segnalazione all'utente nel UI.</t>
+          <t>Campo/sezione non gestito/a in modo strutturato dall’applicativo</t>
         </is>
       </c>
       <c r="L190" s="32" t="n"/>
@@ -12949,10 +13613,14 @@
       </c>
       <c r="K191" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L191" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L191" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M191" s="32" t="n"/>
       <c r="N191" s="32" t="n"/>
       <c r="O191" s="32" t="n"/>
@@ -13006,10 +13674,14 @@
       </c>
       <c r="K192" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L192" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L192" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M192" s="32" t="n"/>
       <c r="N192" s="32" t="n"/>
       <c r="O192" s="32" t="n"/>
@@ -13062,10 +13734,14 @@
       </c>
       <c r="K193" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L193" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L193" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M193" s="32" t="n"/>
       <c r="N193" s="32" t="n"/>
       <c r="O193" s="32" t="n"/>
@@ -13118,10 +13794,14 @@
       </c>
       <c r="K194" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L194" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L194" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M194" s="32" t="n"/>
       <c r="N194" s="32" t="n"/>
       <c r="O194" s="32" t="n"/>
@@ -13174,10 +13854,14 @@
       </c>
       <c r="K195" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L195" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L195" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M195" s="32" t="n"/>
       <c r="N195" s="32" t="n"/>
       <c r="O195" s="32" t="n"/>
@@ -13230,10 +13914,14 @@
       </c>
       <c r="K196" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L196" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L196" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M196" s="32" t="n"/>
       <c r="N196" s="32" t="n"/>
       <c r="O196" s="32" t="n"/>
@@ -13286,10 +13974,14 @@
       </c>
       <c r="K197" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L197" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L197" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M197" s="32" t="n"/>
       <c r="N197" s="32" t="n"/>
       <c r="O197" s="32" t="n"/>
@@ -13342,10 +14034,14 @@
       </c>
       <c r="K198" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L198" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L198" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M198" s="32" t="n"/>
       <c r="N198" s="32" t="n"/>
       <c r="O198" s="32" t="n"/>
@@ -13398,10 +14094,14 @@
       </c>
       <c r="K199" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L199" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L199" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M199" s="32" t="n"/>
       <c r="N199" s="32" t="n"/>
       <c r="O199" s="32" t="n"/>
@@ -13454,10 +14154,14 @@
       </c>
       <c r="K200" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L200" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L200" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M200" s="32" t="n"/>
       <c r="N200" s="32" t="n"/>
       <c r="O200" s="32" t="n"/>
@@ -13510,10 +14214,14 @@
       </c>
       <c r="K201" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L201" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L201" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M201" s="32" t="n"/>
       <c r="N201" s="32" t="n"/>
       <c r="O201" s="32" t="n"/>
@@ -13566,10 +14274,14 @@
       </c>
       <c r="K202" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L202" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L202" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M202" s="32" t="n"/>
       <c r="N202" s="32" t="n"/>
       <c r="O202" s="32" t="n"/>
@@ -13622,10 +14334,14 @@
       </c>
       <c r="K203" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L203" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L203" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M203" s="32" t="n"/>
       <c r="N203" s="32" t="n"/>
       <c r="O203" s="32" t="n"/>
@@ -13681,10 +14397,14 @@
       </c>
       <c r="K204" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L204" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L204" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M204" s="32" t="n"/>
       <c r="N204" s="32" t="n"/>
       <c r="O204" s="32" t="n"/>
@@ -13737,10 +14457,14 @@
       </c>
       <c r="K205" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L205" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L205" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M205" s="32" t="n"/>
       <c r="N205" s="32" t="n"/>
       <c r="O205" s="32" t="n"/>
@@ -13797,10 +14521,14 @@
       </c>
       <c r="K206" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L206" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L206" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M206" s="32" t="n"/>
       <c r="N206" s="32" t="n"/>
       <c r="O206" s="32" t="n"/>
@@ -13853,10 +14581,14 @@
       </c>
       <c r="K207" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L207" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L207" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M207" s="32" t="n"/>
       <c r="N207" s="32" t="n"/>
       <c r="O207" s="32" t="n"/>
@@ -13909,10 +14641,14 @@
       </c>
       <c r="K208" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L208" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L208" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M208" s="32" t="n"/>
       <c r="N208" s="32" t="n"/>
       <c r="O208" s="32" t="n"/>
@@ -13965,10 +14701,14 @@
       </c>
       <c r="K209" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L209" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L209" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M209" s="32" t="n"/>
       <c r="N209" s="32" t="n"/>
       <c r="O209" s="32" t="n"/>
@@ -14021,10 +14761,14 @@
       </c>
       <c r="K210" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L210" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L210" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M210" s="32" t="n"/>
       <c r="N210" s="32" t="n"/>
       <c r="O210" s="32" t="n"/>
@@ -14077,10 +14821,14 @@
       </c>
       <c r="K211" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L211" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L211" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M211" s="32" t="n"/>
       <c r="N211" s="32" t="n"/>
       <c r="O211" s="32" t="n"/>
@@ -14133,10 +14881,14 @@
       </c>
       <c r="K212" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L212" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L212" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M212" s="32" t="n"/>
       <c r="N212" s="32" t="n"/>
       <c r="O212" s="32" t="n"/>
@@ -14189,10 +14941,14 @@
       </c>
       <c r="K213" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L213" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L213" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M213" s="32" t="n"/>
       <c r="N213" s="32" t="n"/>
       <c r="O213" s="32" t="n"/>
@@ -14245,10 +15001,14 @@
       </c>
       <c r="K214" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L214" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L214" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M214" s="32" t="n"/>
       <c r="N214" s="32" t="n"/>
       <c r="O214" s="32" t="n"/>
@@ -14301,10 +15061,14 @@
       </c>
       <c r="K215" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L215" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L215" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M215" s="32" t="n"/>
       <c r="N215" s="32" t="n"/>
       <c r="O215" s="32" t="n"/>
@@ -14357,10 +15121,14 @@
       </c>
       <c r="K216" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L216" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L216" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M216" s="32" t="n"/>
       <c r="N216" s="32" t="n"/>
       <c r="O216" s="32" t="n"/>
@@ -14413,10 +15181,14 @@
       </c>
       <c r="K217" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L217" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L217" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M217" s="32" t="n"/>
       <c r="N217" s="32" t="n"/>
       <c r="O217" s="32" t="n"/>
@@ -14469,10 +15241,14 @@
       </c>
       <c r="K218" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L218" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L218" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M218" s="32" t="n"/>
       <c r="N218" s="32" t="n"/>
       <c r="O218" s="32" t="n"/>
@@ -14528,10 +15304,14 @@
       </c>
       <c r="K219" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L219" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L219" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M219" s="32" t="n"/>
       <c r="N219" s="32" t="n"/>
       <c r="O219" s="32" t="n"/>
@@ -14584,10 +15364,14 @@
       </c>
       <c r="K220" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L220" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L220" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M220" s="32" t="n"/>
       <c r="N220" s="32" t="n"/>
       <c r="O220" s="32" t="n"/>
@@ -14644,10 +15428,14 @@
       </c>
       <c r="K221" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L221" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L221" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M221" s="32" t="n"/>
       <c r="N221" s="32" t="n"/>
       <c r="O221" s="32" t="n"/>
@@ -14700,10 +15488,14 @@
       </c>
       <c r="K222" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L222" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L222" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M222" s="32" t="n"/>
       <c r="N222" s="32" t="n"/>
       <c r="O222" s="32" t="n"/>
@@ -14756,10 +15548,14 @@
       </c>
       <c r="K223" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L223" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L223" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M223" s="32" t="n"/>
       <c r="N223" s="32" t="n"/>
       <c r="O223" s="32" t="n"/>
@@ -14812,10 +15608,14 @@
       </c>
       <c r="K224" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L224" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L224" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M224" s="32" t="n"/>
       <c r="N224" s="32" t="n"/>
       <c r="O224" s="32" t="n"/>
@@ -14868,10 +15668,14 @@
       </c>
       <c r="K225" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L225" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L225" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M225" s="32" t="n"/>
       <c r="N225" s="32" t="n"/>
       <c r="O225" s="32" t="n"/>
@@ -14924,10 +15728,14 @@
       </c>
       <c r="K226" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L226" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L226" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M226" s="32" t="n"/>
       <c r="N226" s="32" t="n"/>
       <c r="O226" s="32" t="n"/>
@@ -14980,10 +15788,14 @@
       </c>
       <c r="K227" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L227" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L227" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M227" s="32" t="n"/>
       <c r="N227" s="32" t="n"/>
       <c r="O227" s="32" t="n"/>
@@ -15036,10 +15848,14 @@
       </c>
       <c r="K228" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L228" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L228" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M228" s="32" t="n"/>
       <c r="N228" s="32" t="n"/>
       <c r="O228" s="32" t="n"/>
@@ -15092,10 +15908,14 @@
       </c>
       <c r="K229" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L229" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L229" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M229" s="32" t="n"/>
       <c r="N229" s="32" t="n"/>
       <c r="O229" s="32" t="n"/>
@@ -15148,10 +15968,14 @@
       </c>
       <c r="K230" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L230" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L230" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M230" s="32" t="n"/>
       <c r="N230" s="32" t="n"/>
       <c r="O230" s="32" t="n"/>
@@ -15204,10 +16028,14 @@
       </c>
       <c r="K231" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L231" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L231" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M231" s="32" t="n"/>
       <c r="N231" s="32" t="n"/>
       <c r="O231" s="32" t="n"/>
@@ -15260,10 +16088,14 @@
       </c>
       <c r="K232" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L232" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L232" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M232" s="32" t="n"/>
       <c r="N232" s="32" t="n"/>
       <c r="O232" s="32" t="n"/>
@@ -15316,10 +16148,14 @@
       </c>
       <c r="K233" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L233" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L233" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M233" s="32" t="n"/>
       <c r="N233" s="32" t="n"/>
       <c r="O233" s="32" t="n"/>
@@ -15375,10 +16211,14 @@
       </c>
       <c r="K234" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L234" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L234" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M234" s="32" t="n"/>
       <c r="N234" s="32" t="n"/>
       <c r="O234" s="32" t="n"/>
@@ -15431,10 +16271,14 @@
       </c>
       <c r="K235" s="32" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L235" s="32" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L235" s="32" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M235" s="32" t="n"/>
       <c r="N235" s="32" t="n"/>
       <c r="O235" s="32" t="n"/>
@@ -15491,10 +16335,14 @@
       </c>
       <c r="K236" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L236" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L236" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M236" s="66" t="n"/>
       <c r="N236" s="66" t="n"/>
       <c r="O236" s="66" t="n"/>
@@ -15547,10 +16395,14 @@
       </c>
       <c r="K237" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L237" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L237" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M237" s="66" t="n"/>
       <c r="N237" s="66" t="n"/>
       <c r="O237" s="66" t="n"/>
@@ -15603,10 +16455,14 @@
       </c>
       <c r="K238" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L238" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L238" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M238" s="66" t="n"/>
       <c r="N238" s="66" t="n"/>
       <c r="O238" s="66" t="n"/>
@@ -15659,10 +16515,14 @@
       </c>
       <c r="K239" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L239" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L239" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M239" s="66" t="n"/>
       <c r="N239" s="66" t="n"/>
       <c r="O239" s="66" t="n"/>
@@ -15715,10 +16575,14 @@
       </c>
       <c r="K240" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L240" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L240" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M240" s="66" t="n"/>
       <c r="N240" s="66" t="n"/>
       <c r="O240" s="66" t="n"/>
@@ -15771,10 +16635,14 @@
       </c>
       <c r="K241" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L241" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L241" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M241" s="66" t="n"/>
       <c r="N241" s="66" t="n"/>
       <c r="O241" s="66" t="n"/>
@@ -15827,10 +16695,14 @@
       </c>
       <c r="K242" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L242" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L242" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M242" s="66" t="n"/>
       <c r="N242" s="66" t="n"/>
       <c r="O242" s="66" t="n"/>
@@ -15883,10 +16755,14 @@
       </c>
       <c r="K243" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L243" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L243" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M243" s="66" t="n"/>
       <c r="N243" s="66" t="n"/>
       <c r="O243" s="66" t="n"/>
@@ -15942,10 +16818,14 @@
       </c>
       <c r="K244" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L244" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L244" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M244" s="66" t="n"/>
       <c r="N244" s="66" t="n"/>
       <c r="O244" s="66" t="n"/>
@@ -15998,10 +16878,14 @@
       </c>
       <c r="K245" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L245" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L245" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M245" s="66" t="n"/>
       <c r="N245" s="66" t="n"/>
       <c r="O245" s="66" t="n"/>
@@ -16058,10 +16942,14 @@
       </c>
       <c r="K246" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L246" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L246" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M246" s="66" t="n"/>
       <c r="N246" s="66" t="n"/>
       <c r="O246" s="66" t="n"/>
@@ -16114,10 +17002,14 @@
       </c>
       <c r="K247" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L247" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L247" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M247" s="66" t="n"/>
       <c r="N247" s="66" t="n"/>
       <c r="O247" s="66" t="n"/>
@@ -16170,10 +17062,14 @@
       </c>
       <c r="K248" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L248" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L248" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M248" s="66" t="n"/>
       <c r="N248" s="66" t="n"/>
       <c r="O248" s="66" t="n"/>
@@ -16226,10 +17122,14 @@
       </c>
       <c r="K249" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L249" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L249" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M249" s="66" t="n"/>
       <c r="N249" s="66" t="n"/>
       <c r="O249" s="66" t="n"/>
@@ -16282,10 +17182,14 @@
       </c>
       <c r="K250" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L250" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L250" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M250" s="66" t="n"/>
       <c r="N250" s="66" t="n"/>
       <c r="O250" s="66" t="n"/>
@@ -16338,10 +17242,14 @@
       </c>
       <c r="K251" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L251" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L251" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M251" s="66" t="n"/>
       <c r="N251" s="66" t="n"/>
       <c r="O251" s="66" t="n"/>
@@ -16394,10 +17302,14 @@
       </c>
       <c r="K252" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L252" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L252" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M252" s="66" t="n"/>
       <c r="N252" s="66" t="n"/>
       <c r="O252" s="66" t="n"/>
@@ -16450,10 +17362,14 @@
       </c>
       <c r="K253" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L253" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L253" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M253" s="66" t="n"/>
       <c r="N253" s="66" t="n"/>
       <c r="O253" s="66" t="n"/>
@@ -16506,10 +17422,14 @@
       </c>
       <c r="K254" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L254" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L254" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M254" s="66" t="n"/>
       <c r="N254" s="66" t="n"/>
       <c r="O254" s="66" t="n"/>
@@ -16562,10 +17482,14 @@
       </c>
       <c r="K255" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L255" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L255" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M255" s="66" t="n"/>
       <c r="N255" s="66" t="n"/>
       <c r="O255" s="66" t="n"/>
@@ -16618,10 +17542,14 @@
       </c>
       <c r="K256" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L256" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L256" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M256" s="66" t="n"/>
       <c r="N256" s="66" t="n"/>
       <c r="O256" s="66" t="n"/>
@@ -16674,10 +17602,14 @@
       </c>
       <c r="K257" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L257" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L257" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M257" s="66" t="n"/>
       <c r="N257" s="66" t="n"/>
       <c r="O257" s="66" t="n"/>
@@ -16730,10 +17662,14 @@
       </c>
       <c r="K258" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L258" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L258" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M258" s="66" t="n"/>
       <c r="N258" s="66" t="n"/>
       <c r="O258" s="66" t="n"/>
@@ -16786,10 +17722,14 @@
       </c>
       <c r="K259" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L259" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L259" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M259" s="66" t="n"/>
       <c r="N259" s="66" t="n"/>
       <c r="O259" s="66" t="n"/>
@@ -16842,10 +17782,14 @@
       </c>
       <c r="K260" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L260" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L260" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M260" s="66" t="n"/>
       <c r="N260" s="66" t="n"/>
       <c r="O260" s="66" t="n"/>
@@ -16898,10 +17842,14 @@
       </c>
       <c r="K261" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L261" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L261" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M261" s="66" t="n"/>
       <c r="N261" s="66" t="n"/>
       <c r="O261" s="66" t="n"/>
@@ -16954,10 +17902,14 @@
       </c>
       <c r="K262" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L262" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L262" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M262" s="66" t="n"/>
       <c r="N262" s="66" t="n"/>
       <c r="O262" s="66" t="n"/>
@@ -17010,10 +17962,14 @@
       </c>
       <c r="K263" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L263" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L263" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M263" s="66" t="n"/>
       <c r="N263" s="66" t="n"/>
       <c r="O263" s="66" t="n"/>
@@ -17069,10 +18025,14 @@
       </c>
       <c r="K264" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L264" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L264" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M264" s="66" t="n"/>
       <c r="N264" s="66" t="n"/>
       <c r="O264" s="66" t="n"/>
@@ -17125,10 +18085,14 @@
       </c>
       <c r="K265" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L265" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L265" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M265" s="66" t="n"/>
       <c r="N265" s="66" t="n"/>
       <c r="O265" s="66" t="n"/>
@@ -17185,10 +18149,14 @@
       </c>
       <c r="K266" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L266" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L266" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M266" s="66" t="n"/>
       <c r="N266" s="66" t="n"/>
       <c r="O266" s="66" t="n"/>
@@ -17241,10 +18209,14 @@
       </c>
       <c r="K267" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L267" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L267" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M267" s="66" t="n"/>
       <c r="N267" s="66" t="n"/>
       <c r="O267" s="66" t="n"/>
@@ -17297,10 +18269,14 @@
       </c>
       <c r="K268" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L268" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L268" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M268" s="66" t="n"/>
       <c r="N268" s="66" t="n"/>
       <c r="O268" s="66" t="n"/>
@@ -17353,10 +18329,14 @@
       </c>
       <c r="K269" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L269" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L269" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M269" s="66" t="n"/>
       <c r="N269" s="66" t="n"/>
       <c r="O269" s="66" t="n"/>
@@ -17409,10 +18389,14 @@
       </c>
       <c r="K270" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L270" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L270" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M270" s="66" t="n"/>
       <c r="N270" s="66" t="n"/>
       <c r="O270" s="66" t="n"/>
@@ -17465,10 +18449,14 @@
       </c>
       <c r="K271" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L271" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L271" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M271" s="66" t="n"/>
       <c r="N271" s="66" t="n"/>
       <c r="O271" s="66" t="n"/>
@@ -17521,10 +18509,14 @@
       </c>
       <c r="K272" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L272" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L272" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M272" s="66" t="n"/>
       <c r="N272" s="66" t="n"/>
       <c r="O272" s="66" t="n"/>
@@ -17577,10 +18569,14 @@
       </c>
       <c r="K273" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L273" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L273" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M273" s="66" t="n"/>
       <c r="N273" s="66" t="n"/>
       <c r="O273" s="66" t="n"/>
@@ -17633,10 +18629,14 @@
       </c>
       <c r="K274" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L274" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L274" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M274" s="66" t="n"/>
       <c r="N274" s="66" t="n"/>
       <c r="O274" s="66" t="n"/>
@@ -17689,10 +18689,14 @@
       </c>
       <c r="K275" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L275" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L275" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M275" s="66" t="n"/>
       <c r="N275" s="66" t="n"/>
       <c r="O275" s="66" t="n"/>
@@ -17745,10 +18749,14 @@
       </c>
       <c r="K276" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L276" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L276" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M276" s="66" t="n"/>
       <c r="N276" s="66" t="n"/>
       <c r="O276" s="66" t="n"/>
@@ -17801,10 +18809,14 @@
       </c>
       <c r="K277" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L277" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L277" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M277" s="66" t="n"/>
       <c r="N277" s="66" t="n"/>
       <c r="O277" s="66" t="n"/>
@@ -17857,10 +18869,14 @@
       </c>
       <c r="K278" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L278" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L278" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M278" s="66" t="n"/>
       <c r="N278" s="66" t="n"/>
       <c r="O278" s="66" t="n"/>
@@ -17913,10 +18929,14 @@
       </c>
       <c r="K279" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L279" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L279" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M279" s="66" t="n"/>
       <c r="N279" s="66" t="n"/>
       <c r="O279" s="66" t="n"/>
@@ -17969,10 +18989,14 @@
       </c>
       <c r="K280" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L280" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L280" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M280" s="66" t="n"/>
       <c r="N280" s="66" t="n"/>
       <c r="O280" s="66" t="n"/>
@@ -18025,10 +19049,14 @@
       </c>
       <c r="K281" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L281" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L281" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M281" s="66" t="n"/>
       <c r="N281" s="66" t="n"/>
       <c r="O281" s="66" t="n"/>
@@ -18081,10 +19109,14 @@
       </c>
       <c r="K282" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L282" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L282" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M282" s="66" t="n"/>
       <c r="N282" s="66" t="n"/>
       <c r="O282" s="66" t="n"/>
@@ -18137,10 +19169,14 @@
       </c>
       <c r="K283" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L283" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L283" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M283" s="66" t="n"/>
       <c r="N283" s="66" t="n"/>
       <c r="O283" s="66" t="n"/>
@@ -18196,10 +19232,14 @@
       </c>
       <c r="K284" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L284" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L284" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M284" s="66" t="n"/>
       <c r="N284" s="66" t="n"/>
       <c r="O284" s="66" t="n"/>
@@ -18252,10 +19292,14 @@
       </c>
       <c r="K285" s="66" t="inlineStr">
         <is>
-          <t>Software non gestisce questa tipologia documentale/scenario. ConsensoSicuro v1.0.0 supporta esclusivamente RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione, scenario OK rappresentato dal test 448 (CT24).</t>
-        </is>
-      </c>
-      <c r="L285" s="66" t="n"/>
+          <t>Altro (specificare)</t>
+        </is>
+      </c>
+      <c r="L285" s="66" t="inlineStr">
+        <is>
+          <t>Tipologia documentale non gestita dall'applicativo: ConsensoSicuro v1.0.0 supporta esclusivamente il CDA2 RSA (Referto di Specialistica Ambulatoriale) per il servizio di Validazione — test 448 (CT24).</t>
+        </is>
+      </c>
       <c r="M285" s="66" t="n"/>
       <c r="N285" s="66" t="n"/>
       <c r="O285" s="66" t="n"/>
